--- a/blocks_trajectory_gt_confusion.xlsx
+++ b/blocks_trajectory_gt_confusion.xlsx
@@ -65,7 +65,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,12 +146,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -775,62 +786,62 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1315,7 @@
           <t>holding(x)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1321,7 +1332,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1356,7 +1367,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1380,7 +1391,7 @@
           <t>clear(x)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1397,7 +1408,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1432,7 +1443,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1449,204 +1460,204 @@
           <t>handempty()</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ontable(x)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (absent from next state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>holding(x)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=3</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=3</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=4</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=5</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ontable(x)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>TP=4 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>holding(x)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1658,7 +1669,7 @@
           <t>N transitions</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
@@ -1667,7 +1678,7 @@
       <c r="E16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
@@ -1685,7 +1696,7 @@
       <c r="K16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="L16" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,62 +2056,62 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -2118,61 +2129,71 @@
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>TP=3 FP=0
-FN=0 TN=0</t>
+FN=0 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=2 TN=0</t>
+FN=2 TN=0
+SW=1</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=1 TN=0</t>
+FN=1 TN=0
+SW=1</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=1 TN=0</t>
+FN=1 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=3 TN=0</t>
+FN=3 TN=0
+SW=3</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=1 TN=0</t>
+FN=1 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=4 TN=0</t>
+FN=4 TN=0
+SW=1</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=2 TN=0</t>
+FN=2 TN=0
+SW=2</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=4 TN=0</t>
+FN=4 TN=0
+SW=3</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>TP=3 FP=0
-FN=1 TN=0</t>
+FN=1 TN=0
+SW=1</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2516,7 @@
           <t>on(x,y)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2503,16 +2524,18 @@
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=0 TN=0</t>
+FN=0 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2520,34 +2543,39 @@
       <c r="G6" s="5" t="inlineStr">
         <is>
           <t>TP=4 FP=0
-FN=0 TN=0</t>
+FN=0 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=0 TN=0</t>
+FN=0 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=0 TN=0</t>
+FN=0 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
           <t>TP=4 FP=0
-FN=1 TN=0</t>
+FN=1 TN=0
+SW=0</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
           <t>TP=2 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+FN=2 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2564,7 +2592,7 @@
           <t>clear(x)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2581,7 +2609,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2616,7 +2644,7 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2633,349 +2661,349 @@
           <t>handempty()</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ADD EFFECTS (in next state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>holding(x)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>clear(y)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (absent from next state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>clear(x)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=2</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=5</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>handempty()</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=4</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=2</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=2</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=5</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=4</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ADD EFFECTS (in next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>holding(x)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>TP=4 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>TP=4 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>clear(y)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>on(x,y)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>clear(x)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2989,10 +3017,10 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>handempty()</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+          <t>on(x,y)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3000,16 +3028,18 @@
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=2</t>
+FN=0 TN=2
+SW=0</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+FN=0 TN=1
+SW=0</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3017,34 +3047,39 @@
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=4</t>
+FN=0 TN=4
+SW=0</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=2</t>
+FN=0 TN=2
+SW=0</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=2</t>
+FN=0 TN=2
+SW=0</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=5</t>
+FN=0 TN=5
+SW=0</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+FN=0 TN=4
+SW=0</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3056,7 +3091,7 @@
           <t>N transitions</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -3065,7 +3100,7 @@
       <c r="E19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
@@ -3083,7 +3118,7 @@
       <c r="K19" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L19" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3124,14 +3159,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>FA violation = fluent differing from GT in next_state, whose objects are NOT a subset of action params. Predicate counts from GT next_state.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>SUMMARY PER PROBLEM</t>
         </is>
@@ -3176,6 +3211,11 @@
           <t>FA %</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Non-FA %</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3203,6 +3243,11 @@
           <t>100.0%</t>
         </is>
       </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3230,6 +3275,11 @@
           <t>47.1%</t>
         </is>
       </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -3257,58 +3307,73 @@
           <t>71.4%</t>
         </is>
       </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>problem4</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>85.7%</t>
         </is>
       </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>problem5</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>69.4%</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -3338,148 +3403,177 @@
           <t>61.5%</t>
         </is>
       </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>problem7</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="13" t="n">
         <v>144</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>68.5%</t>
         </is>
       </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>31.5%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>problem8</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="13" t="n">
         <v>94</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>86.2%</t>
         </is>
       </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>13.8%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>problem9</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="13" t="n">
         <v>188</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="13" t="n">
         <v>84</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>82.1%</t>
         </is>
       </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>problem10</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="14">
         <f>SUM(B6:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="14">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="14">
         <f>SUM(D6:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <f>SUM(E6:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="14">
         <f>SUM(F6:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="14">
         <f>IF(D16&gt;0,TEXT(E16/D16*100,"0.0")&amp;"%","0%")</f>
         <v/>
       </c>
+      <c r="H16" s="14">
+        <f>IF(D16&gt;0,TEXT(F16/D16*100,"0.0")&amp;"%","0%")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>PROBLEM1 — 6 transitions, 39 predicates, 2 FA violations</t>
         </is>
@@ -3619,62 +3713,62 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>stack c b</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>pick_up d</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -3712,7 +3806,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>PROBLEM2 — 8 transitions, 53 predicates, 8 FA violations</t>
         </is>
@@ -3759,74 +3853,74 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>unstack d c</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>clear a</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>ontable a</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>put_down d</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -3895,117 +3989,117 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>pick_up a</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>stack a c</t>
         </is>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -4043,7 +4137,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>PROBLEM3 — 8 transitions, 63 predicates, 5 FA violations</t>
         </is>
@@ -4152,31 +4246,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>pick_up a</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -4214,67 +4308,67 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>unstack d e</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C50" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="11" t="n">
+      <c r="E50" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>on a c</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -4374,7 +4468,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>PROBLEM4 — 6 transitions, 45 predicates, 12 FA violations</t>
         </is>
@@ -4483,201 +4577,201 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C63" s="11" t="n">
+      <c r="C63" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E63" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>stack b c</t>
         </is>
       </c>
-      <c r="C67" s="11" t="n">
+      <c r="C67" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E67" s="11" t="n">
+      <c r="E67" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>pick_up a</t>
         </is>
       </c>
-      <c r="C70" s="11" t="n">
+      <c r="C70" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E70" s="11" t="n">
+      <c r="E70" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="F71" s="11" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="F72" s="11" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="F73" s="11" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -4715,7 +4809,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="A78" s="15" t="inlineStr">
         <is>
           <t>PROBLEM5 — 10 transitions, 72 predicates, 25 FA violations</t>
         </is>
@@ -4793,184 +4887,184 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>put_down a</t>
         </is>
       </c>
-      <c r="C81" s="11" t="n">
+      <c r="C81" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E81" s="11" t="n">
+      <c r="E81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F81" s="11" t="inlineStr">
+      <c r="F81" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G81" s="11" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="F82" s="11" t="inlineStr">
+      <c r="F82" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="F83" s="11" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="F84" s="11" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>unstack b c</t>
         </is>
       </c>
-      <c r="C85" s="11" t="n">
+      <c r="C85" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E85" s="11" t="n">
+      <c r="E85" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F85" s="11" t="inlineStr">
+      <c r="F85" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G85" s="11" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="F86" s="11" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G86" s="11" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="F87" s="11" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G87" s="11" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="inlineStr">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>stack b a</t>
         </is>
       </c>
-      <c r="C88" s="11" t="n">
+      <c r="C88" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D88" s="11" t="n">
+      <c r="D88" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="11" t="n">
+      <c r="E88" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G88" s="11" t="inlineStr">
+      <c r="G88" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>unstack c d</t>
         </is>
       </c>
-      <c r="C89" s="11" t="n">
+      <c r="C89" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E89" s="11" t="n">
+      <c r="E89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="11" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G89" s="11" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -5008,158 +5102,158 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="inlineStr">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>unstack d e</t>
         </is>
       </c>
-      <c r="C91" s="11" t="n">
+      <c r="C91" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E91" s="11" t="n">
+      <c r="E91" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F91" s="11" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G91" s="11" t="inlineStr">
+      <c r="G91" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="F92" s="11" t="inlineStr">
+      <c r="F92" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="G92" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="F93" s="11" t="inlineStr">
+      <c r="F93" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G93" s="11" t="inlineStr">
+      <c r="G93" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="F94" s="11" t="inlineStr">
+      <c r="F94" s="13" t="inlineStr">
         <is>
           <t>on c b</t>
         </is>
       </c>
-      <c r="G94" s="11" t="inlineStr">
+      <c r="G94" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="F95" s="11" t="inlineStr">
+      <c r="F95" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G95" s="11" t="inlineStr">
+      <c r="G95" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="F96" s="11" t="inlineStr">
+      <c r="F96" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G96" s="11" t="inlineStr">
+      <c r="G96" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="inlineStr">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B97" s="13" t="inlineStr">
         <is>
           <t>stack d c</t>
         </is>
       </c>
-      <c r="C97" s="11" t="n">
+      <c r="C97" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D97" s="11" t="n">
+      <c r="D97" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E97" s="11" t="n">
+      <c r="E97" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F97" s="11" t="inlineStr">
+      <c r="F97" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="F98" s="11" t="inlineStr">
+      <c r="F98" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="F99" s="11" t="inlineStr">
+      <c r="F99" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="F100" s="11" t="inlineStr">
+      <c r="F100" s="13" t="inlineStr">
         <is>
           <t>on c b</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -5197,98 +5291,98 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="inlineStr">
+      <c r="A102" s="13" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>stack e d</t>
         </is>
       </c>
-      <c r="C102" s="11" t="n">
+      <c r="C102" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D102" s="11" t="n">
+      <c r="D102" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="E102" s="11" t="n">
+      <c r="E102" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="F102" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G102" s="11" t="inlineStr">
+      <c r="G102" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="F103" s="11" t="inlineStr">
+      <c r="F103" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="F104" s="11" t="inlineStr">
+      <c r="F104" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="F105" s="11" t="inlineStr">
+      <c r="F105" s="13" t="inlineStr">
         <is>
           <t>on c b</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="F106" s="11" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="F107" s="11" t="inlineStr">
+      <c r="F107" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="13" t="inlineStr">
+      <c r="A110" s="15" t="inlineStr">
         <is>
           <t>PROBLEM6 — 9 transitions, 83 predicates, 8 FA violations</t>
         </is>
@@ -5366,43 +5460,43 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="inlineStr">
+      <c r="A113" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>unstack a b</t>
         </is>
       </c>
-      <c r="C113" s="11" t="n">
+      <c r="C113" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E113" s="11" t="n">
+      <c r="E113" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="F113" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G113" s="11" t="inlineStr">
+      <c r="G113" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="F114" s="11" t="inlineStr">
+      <c r="F114" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G114" s="11" t="inlineStr">
+      <c r="G114" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -5564,117 +5658,117 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B120" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C120" s="11" t="n">
+      <c r="C120" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E120" s="11" t="n">
+      <c r="E120" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F120" s="11" t="inlineStr">
+      <c r="F120" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G120" s="11" t="inlineStr">
+      <c r="G120" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F121" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="G121" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F122" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G122" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="inlineStr">
+      <c r="A123" s="13" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B123" s="13" t="inlineStr">
         <is>
           <t>stack b a</t>
         </is>
       </c>
-      <c r="C123" s="11" t="n">
+      <c r="C123" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E123" s="11" t="n">
+      <c r="E123" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F123" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="G123" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="F124" s="11" t="inlineStr">
+      <c r="F124" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="F125" s="11" t="inlineStr">
+      <c r="F125" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G125" s="11" t="inlineStr">
+      <c r="G125" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="13" t="inlineStr">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>PROBLEM7 — 15 transitions, 144 predicates, 37 FA violations</t>
         </is>
@@ -5752,98 +5846,98 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="inlineStr">
+      <c r="A131" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B131" s="13" t="inlineStr">
         <is>
           <t>unstack a b</t>
         </is>
       </c>
-      <c r="C131" s="11" t="n">
+      <c r="C131" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="11" t="n">
+      <c r="E131" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F131" s="11" t="inlineStr">
+      <c r="F131" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="F132" s="11" t="inlineStr">
+      <c r="F132" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B133" s="13" t="inlineStr">
         <is>
           <t>put_down a</t>
         </is>
       </c>
-      <c r="C133" s="11" t="n">
+      <c r="C133" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E133" s="11" t="n">
+      <c r="E133" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="F133" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G133" s="11" t="inlineStr">
+      <c r="G133" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="F134" s="11" t="inlineStr">
+      <c r="F134" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G134" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="F135" s="11" t="inlineStr">
+      <c r="F135" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G135" s="11" t="inlineStr">
+      <c r="G135" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -5912,536 +6006,536 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="inlineStr">
+      <c r="A138" s="13" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>pick_up d</t>
         </is>
       </c>
-      <c r="C138" s="11" t="n">
+      <c r="C138" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D138" s="11" t="n">
+      <c r="D138" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E138" s="11" t="n">
+      <c r="E138" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F138" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G138" s="11" t="inlineStr">
+      <c r="G138" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F139" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G139" s="11" t="inlineStr">
+      <c r="G139" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="11" t="inlineStr">
+      <c r="A140" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B140" s="13" t="inlineStr">
         <is>
           <t>stack d e</t>
         </is>
       </c>
-      <c r="C140" s="11" t="n">
+      <c r="C140" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D140" s="11" t="n">
+      <c r="D140" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E140" s="11" t="n">
+      <c r="E140" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F140" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G140" s="11" t="inlineStr">
+      <c r="G140" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="F141" s="11" t="inlineStr">
+      <c r="F141" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G141" s="11" t="inlineStr">
+      <c r="G141" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="F142" s="11" t="inlineStr">
+      <c r="F142" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G142" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="11" t="inlineStr">
+      <c r="A143" s="13" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B143" s="13" t="inlineStr">
         <is>
           <t>unstack b c</t>
         </is>
       </c>
-      <c r="C143" s="11" t="n">
+      <c r="C143" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D143" s="11" t="n">
+      <c r="D143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E143" s="11" t="n">
+      <c r="E143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F143" s="11" t="inlineStr">
+      <c r="F143" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G143" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="F144" s="11" t="inlineStr">
+      <c r="F144" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="F145" s="11" t="inlineStr">
+      <c r="F145" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G145" s="11" t="inlineStr">
+      <c r="G145" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="F146" s="11" t="inlineStr">
+      <c r="F146" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G146" s="11" t="inlineStr">
+      <c r="G146" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="11" t="inlineStr">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B147" s="11" t="inlineStr">
+      <c r="B147" s="13" t="inlineStr">
         <is>
           <t>put_down b</t>
         </is>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C147" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D147" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E147" s="11" t="n">
+      <c r="E147" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F147" s="11" t="inlineStr">
+      <c r="F147" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G147" s="11" t="inlineStr">
+      <c r="G147" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="F148" s="11" t="inlineStr">
+      <c r="F148" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G148" s="11" t="inlineStr">
+      <c r="G148" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="F149" s="11" t="inlineStr">
+      <c r="F149" s="13" t="inlineStr">
         <is>
           <t>on d f</t>
         </is>
       </c>
-      <c r="G149" s="11" t="inlineStr">
+      <c r="G149" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="F150" s="11" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G150" s="11" t="inlineStr">
+      <c r="G150" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="F151" s="11" t="inlineStr">
+      <c r="F151" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G151" s="11" t="inlineStr">
+      <c r="G151" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="11" t="inlineStr">
+      <c r="A152" s="13" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B152" s="11" t="inlineStr">
+      <c r="B152" s="13" t="inlineStr">
         <is>
           <t>pick_up c</t>
         </is>
       </c>
-      <c r="C152" s="11" t="n">
+      <c r="C152" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D152" s="11" t="n">
+      <c r="D152" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E152" s="11" t="n">
+      <c r="E152" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F152" s="11" t="inlineStr">
+      <c r="F152" s="13" t="inlineStr">
         <is>
           <t>on d f</t>
         </is>
       </c>
-      <c r="G152" s="11" t="inlineStr">
+      <c r="G152" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="inlineStr">
+      <c r="A153" s="13" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B153" s="11" t="inlineStr">
+      <c r="B153" s="13" t="inlineStr">
         <is>
           <t>stack c d</t>
         </is>
       </c>
-      <c r="C153" s="11" t="n">
+      <c r="C153" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D153" s="11" t="n">
+      <c r="D153" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E153" s="11" t="n">
+      <c r="E153" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F153" s="11" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G153" s="11" t="inlineStr">
+      <c r="G153" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="F154" s="11" t="inlineStr">
+      <c r="F154" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G154" s="11" t="inlineStr">
+      <c r="G154" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="F155" s="11" t="inlineStr">
+      <c r="F155" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G155" s="11" t="inlineStr">
+      <c r="G155" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="inlineStr">
+      <c r="A156" s="13" t="inlineStr">
         <is>
           <t>T11</t>
         </is>
       </c>
-      <c r="B156" s="11" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C156" s="11" t="n">
+      <c r="C156" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D156" s="11" t="n">
+      <c r="D156" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E156" s="11" t="n">
+      <c r="E156" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F156" s="11" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G156" s="11" t="inlineStr">
+      <c r="G156" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="F157" s="11" t="inlineStr">
+      <c r="F157" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G157" s="11" t="inlineStr">
+      <c r="G157" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="F158" s="11" t="inlineStr">
+      <c r="F158" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G158" s="11" t="inlineStr">
+      <c r="G158" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="F159" s="11" t="inlineStr">
+      <c r="F159" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G159" s="11" t="inlineStr">
+      <c r="G159" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="F160" s="11" t="inlineStr">
+      <c r="F160" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G160" s="11" t="inlineStr">
+      <c r="G160" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="F161" s="11" t="inlineStr">
+      <c r="F161" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G161" s="11" t="inlineStr">
+      <c r="G161" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="inlineStr">
+      <c r="A162" s="13" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="B162" s="11" t="inlineStr">
+      <c r="B162" s="13" t="inlineStr">
         <is>
           <t>stack b c</t>
         </is>
       </c>
-      <c r="C162" s="11" t="n">
+      <c r="C162" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D162" s="11" t="n">
+      <c r="D162" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E162" s="11" t="n">
+      <c r="E162" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F162" s="11" t="inlineStr">
+      <c r="F162" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G162" s="11" t="inlineStr">
+      <c r="G162" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="F163" s="11" t="inlineStr">
+      <c r="F163" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G163" s="11" t="inlineStr">
+      <c r="G163" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="F164" s="11" t="inlineStr">
+      <c r="F164" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G164" s="11" t="inlineStr">
+      <c r="G164" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="F165" s="11" t="inlineStr">
+      <c r="F165" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G165" s="11" t="inlineStr">
+      <c r="G165" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="F166" s="11" t="inlineStr">
+      <c r="F166" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G166" s="11" t="inlineStr">
+      <c r="G166" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="F167" s="11" t="inlineStr">
+      <c r="F167" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G167" s="11" t="inlineStr">
+      <c r="G167" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="F168" s="11" t="inlineStr">
+      <c r="F168" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G168" s="11" t="inlineStr">
+      <c r="G168" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="F169" s="11" t="inlineStr">
+      <c r="F169" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G169" s="11" t="inlineStr">
+      <c r="G169" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -6510,7 +6604,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="13" t="inlineStr">
+      <c r="A174" s="15" t="inlineStr">
         <is>
           <t>PROBLEM8 — 16 transitions, 150 predicates, 81 FA violations</t>
         </is>
@@ -6588,369 +6682,369 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="11" t="inlineStr">
+      <c r="A177" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B177" s="11" t="inlineStr">
+      <c r="B177" s="13" t="inlineStr">
         <is>
           <t>put_down a</t>
         </is>
       </c>
-      <c r="C177" s="11" t="n">
+      <c r="C177" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D177" s="11" t="n">
+      <c r="D177" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E177" s="11" t="n">
+      <c r="E177" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="F177" s="11" t="inlineStr">
+      <c r="F177" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G177" s="11" t="inlineStr">
+      <c r="G177" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="F178" s="11" t="inlineStr">
+      <c r="F178" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G178" s="11" t="inlineStr">
+      <c r="G178" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="F179" s="11" t="inlineStr">
+      <c r="F179" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G179" s="11" t="inlineStr">
+      <c r="G179" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="F180" s="11" t="inlineStr">
+      <c r="F180" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G180" s="11" t="inlineStr">
+      <c r="G180" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="F181" s="11" t="inlineStr">
+      <c r="F181" s="13" t="inlineStr">
         <is>
           <t>on b c</t>
         </is>
       </c>
-      <c r="G181" s="11" t="inlineStr">
+      <c r="G181" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="F182" s="11" t="inlineStr">
+      <c r="F182" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G182" s="11" t="inlineStr">
+      <c r="G182" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="F183" s="11" t="inlineStr">
+      <c r="F183" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G183" s="11" t="inlineStr">
+      <c r="G183" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="F184" s="11" t="inlineStr">
+      <c r="F184" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G184" s="11" t="inlineStr">
+      <c r="G184" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="F185" s="11" t="inlineStr">
+      <c r="F185" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G185" s="11" t="inlineStr">
+      <c r="G185" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="F186" s="11" t="inlineStr">
+      <c r="F186" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G186" s="11" t="inlineStr">
+      <c r="G186" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="F187" s="11" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G187" s="11" t="inlineStr">
+      <c r="G187" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="F188" s="11" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G188" s="11" t="inlineStr">
+      <c r="G188" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="11" t="inlineStr">
+      <c r="A189" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B189" s="11" t="inlineStr">
+      <c r="B189" s="13" t="inlineStr">
         <is>
           <t>unstack b c</t>
         </is>
       </c>
-      <c r="C189" s="11" t="n">
+      <c r="C189" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D189" s="11" t="n">
+      <c r="D189" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E189" s="11" t="n">
+      <c r="E189" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F189" s="11" t="inlineStr">
+      <c r="F189" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G189" s="11" t="inlineStr">
+      <c r="G189" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="F190" s="11" t="inlineStr">
+      <c r="F190" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G190" s="11" t="inlineStr">
+      <c r="G190" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="F191" s="11" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G191" s="11" t="inlineStr">
+      <c r="G191" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="F192" s="11" t="inlineStr">
+      <c r="F192" s="13" t="inlineStr">
         <is>
           <t>on e d</t>
         </is>
       </c>
-      <c r="G192" s="11" t="inlineStr">
+      <c r="G192" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="F193" s="11" t="inlineStr">
+      <c r="F193" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G193" s="11" t="inlineStr">
+      <c r="G193" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="F194" s="11" t="inlineStr">
+      <c r="F194" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G194" s="11" t="inlineStr">
+      <c r="G194" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="inlineStr">
+      <c r="A195" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B195" s="11" t="inlineStr">
+      <c r="B195" s="13" t="inlineStr">
         <is>
           <t>put_down b</t>
         </is>
       </c>
-      <c r="C195" s="11" t="n">
+      <c r="C195" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D195" s="11" t="n">
+      <c r="D195" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="E195" s="11" t="n">
+      <c r="E195" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F195" s="11" t="inlineStr">
+      <c r="F195" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G195" s="11" t="inlineStr">
+      <c r="G195" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="F196" s="11" t="inlineStr">
+      <c r="F196" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G196" s="11" t="inlineStr">
+      <c r="G196" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="F197" s="11" t="inlineStr">
+      <c r="F197" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G197" s="11" t="inlineStr">
+      <c r="G197" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="F198" s="11" t="inlineStr">
+      <c r="F198" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G198" s="11" t="inlineStr">
+      <c r="G198" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="F199" s="11" t="inlineStr">
+      <c r="F199" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G199" s="11" t="inlineStr">
+      <c r="G199" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="F200" s="11" t="inlineStr">
+      <c r="F200" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G200" s="11" t="inlineStr">
+      <c r="G200" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="F201" s="11" t="inlineStr">
+      <c r="F201" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G201" s="11" t="inlineStr">
+      <c r="G201" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="F202" s="11" t="inlineStr">
+      <c r="F202" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G202" s="11" t="inlineStr">
+      <c r="G202" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
@@ -6988,876 +7082,876 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="11" t="inlineStr">
+      <c r="A204" s="13" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B204" s="11" t="inlineStr">
+      <c r="B204" s="13" t="inlineStr">
         <is>
           <t>put_down c</t>
         </is>
       </c>
-      <c r="C204" s="11" t="n">
+      <c r="C204" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D204" s="11" t="n">
+      <c r="D204" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E204" s="11" t="n">
+      <c r="E204" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F204" s="11" t="inlineStr">
+      <c r="F204" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G204" s="11" t="inlineStr">
+      <c r="G204" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="F205" s="11" t="inlineStr">
+      <c r="F205" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G205" s="11" t="inlineStr">
+      <c r="G205" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="F206" s="11" t="inlineStr">
+      <c r="F206" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G206" s="11" t="inlineStr">
+      <c r="G206" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="F207" s="11" t="inlineStr">
+      <c r="F207" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G207" s="11" t="inlineStr">
+      <c r="G207" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="F208" s="11" t="inlineStr">
+      <c r="F208" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G208" s="11" t="inlineStr">
+      <c r="G208" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="F209" s="11" t="inlineStr">
+      <c r="F209" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G209" s="11" t="inlineStr">
+      <c r="G209" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="11" t="inlineStr">
+      <c r="A210" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B210" s="11" t="inlineStr">
+      <c r="B210" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C210" s="11" t="n">
+      <c r="C210" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D210" s="11" t="n">
+      <c r="D210" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E210" s="11" t="n">
+      <c r="E210" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F210" s="11" t="inlineStr">
+      <c r="F210" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G210" s="11" t="inlineStr">
+      <c r="G210" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="F211" s="11" t="inlineStr">
+      <c r="F211" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G211" s="11" t="inlineStr">
+      <c r="G211" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="F212" s="11" t="inlineStr">
+      <c r="F212" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G212" s="11" t="inlineStr">
+      <c r="G212" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="F213" s="11" t="inlineStr">
+      <c r="F213" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G213" s="11" t="inlineStr">
+      <c r="G213" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="F214" s="11" t="inlineStr">
+      <c r="F214" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G214" s="11" t="inlineStr">
+      <c r="G214" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="F215" s="11" t="inlineStr">
+      <c r="F215" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G215" s="11" t="inlineStr">
+      <c r="G215" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="11" t="inlineStr">
+      <c r="A216" s="13" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B216" s="11" t="inlineStr">
+      <c r="B216" s="13" t="inlineStr">
         <is>
           <t>stack b a</t>
         </is>
       </c>
-      <c r="C216" s="11" t="n">
+      <c r="C216" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D216" s="11" t="n">
+      <c r="D216" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E216" s="11" t="n">
+      <c r="E216" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F216" s="11" t="inlineStr">
+      <c r="F216" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G216" s="11" t="inlineStr">
+      <c r="G216" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="F217" s="11" t="inlineStr">
+      <c r="F217" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G217" s="11" t="inlineStr">
+      <c r="G217" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="F218" s="11" t="inlineStr">
+      <c r="F218" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G218" s="11" t="inlineStr">
+      <c r="G218" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="F219" s="11" t="inlineStr">
+      <c r="F219" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G219" s="11" t="inlineStr">
+      <c r="G219" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="inlineStr">
+      <c r="A220" s="13" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B220" s="11" t="inlineStr">
+      <c r="B220" s="13" t="inlineStr">
         <is>
           <t>unstack d e</t>
         </is>
       </c>
-      <c r="C220" s="11" t="n">
+      <c r="C220" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D220" s="11" t="n">
+      <c r="D220" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E220" s="11" t="n">
+      <c r="E220" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F220" s="11" t="inlineStr">
+      <c r="F220" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G220" s="11" t="inlineStr">
+      <c r="G220" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="F221" s="11" t="inlineStr">
+      <c r="F221" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G221" s="11" t="inlineStr">
+      <c r="G221" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="F222" s="11" t="inlineStr">
+      <c r="F222" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G222" s="11" t="inlineStr">
+      <c r="G222" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="F223" s="11" t="inlineStr">
+      <c r="F223" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G223" s="11" t="inlineStr">
+      <c r="G223" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="inlineStr">
+      <c r="A224" s="13" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B224" s="11" t="inlineStr">
+      <c r="B224" s="13" t="inlineStr">
         <is>
           <t>put_down d</t>
         </is>
       </c>
-      <c r="C224" s="11" t="n">
+      <c r="C224" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D224" s="11" t="n">
+      <c r="D224" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E224" s="11" t="n">
+      <c r="E224" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F224" s="11" t="inlineStr">
+      <c r="F224" s="13" t="inlineStr">
         <is>
           <t>clear b</t>
         </is>
       </c>
-      <c r="G224" s="11" t="inlineStr">
+      <c r="G224" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="F225" s="11" t="inlineStr">
+      <c r="F225" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G225" s="11" t="inlineStr">
+      <c r="G225" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="F226" s="11" t="inlineStr">
+      <c r="F226" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G226" s="11" t="inlineStr">
+      <c r="G226" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="F227" s="11" t="inlineStr">
+      <c r="F227" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G227" s="11" t="inlineStr">
+      <c r="G227" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="F228" s="11" t="inlineStr">
+      <c r="F228" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G228" s="11" t="inlineStr">
+      <c r="G228" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="F229" s="11" t="inlineStr">
+      <c r="F229" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G229" s="11" t="inlineStr">
+      <c r="G229" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="F230" s="11" t="inlineStr">
+      <c r="F230" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G230" s="11" t="inlineStr">
+      <c r="G230" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="inlineStr">
+      <c r="A231" s="13" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B231" s="11" t="inlineStr">
+      <c r="B231" s="13" t="inlineStr">
         <is>
           <t>unstack e f</t>
         </is>
       </c>
-      <c r="C231" s="11" t="n">
+      <c r="C231" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D231" s="11" t="n">
+      <c r="D231" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E231" s="11" t="n">
+      <c r="E231" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F231" s="11" t="inlineStr">
+      <c r="F231" s="13" t="inlineStr">
         <is>
           <t>clear b</t>
         </is>
       </c>
-      <c r="G231" s="11" t="inlineStr">
+      <c r="G231" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="F232" s="11" t="inlineStr">
+      <c r="F232" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G232" s="11" t="inlineStr">
+      <c r="G232" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="F233" s="11" t="inlineStr">
+      <c r="F233" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G233" s="11" t="inlineStr">
+      <c r="G233" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="F234" s="11" t="inlineStr">
+      <c r="F234" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G234" s="11" t="inlineStr">
+      <c r="G234" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="inlineStr">
+      <c r="A235" s="13" t="inlineStr">
         <is>
           <t>T11</t>
         </is>
       </c>
-      <c r="B235" s="11" t="inlineStr">
+      <c r="B235" s="13" t="inlineStr">
         <is>
           <t>stack e d</t>
         </is>
       </c>
-      <c r="C235" s="11" t="n">
+      <c r="C235" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D235" s="11" t="n">
+      <c r="D235" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E235" s="11" t="n">
+      <c r="E235" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F235" s="11" t="inlineStr">
+      <c r="F235" s="13" t="inlineStr">
         <is>
           <t>clear a</t>
         </is>
       </c>
-      <c r="G235" s="11" t="inlineStr">
+      <c r="G235" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="F236" s="11" t="inlineStr">
+      <c r="F236" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G236" s="11" t="inlineStr">
+      <c r="G236" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="11" t="inlineStr">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="B237" s="11" t="inlineStr">
+      <c r="B237" s="13" t="inlineStr">
         <is>
           <t>pick_up f</t>
         </is>
       </c>
-      <c r="C237" s="11" t="n">
+      <c r="C237" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D237" s="11" t="n">
+      <c r="D237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E237" s="11" t="n">
+      <c r="E237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F237" s="11" t="inlineStr">
+      <c r="F237" s="13" t="inlineStr">
         <is>
           <t>clear b</t>
         </is>
       </c>
-      <c r="G237" s="11" t="inlineStr">
+      <c r="G237" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="F238" s="11" t="inlineStr">
+      <c r="F238" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G238" s="11" t="inlineStr">
+      <c r="G238" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="F239" s="11" t="inlineStr">
+      <c r="F239" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G239" s="11" t="inlineStr">
+      <c r="G239" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="F240" s="11" t="inlineStr">
+      <c r="F240" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G240" s="11" t="inlineStr">
+      <c r="G240" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="F241" s="11" t="inlineStr">
+      <c r="F241" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G241" s="11" t="inlineStr">
+      <c r="G241" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="11" t="inlineStr">
+      <c r="A242" s="13" t="inlineStr">
         <is>
           <t>T13</t>
         </is>
       </c>
-      <c r="B242" s="11" t="inlineStr">
+      <c r="B242" s="13" t="inlineStr">
         <is>
           <t>stack f e</t>
         </is>
       </c>
-      <c r="C242" s="11" t="n">
+      <c r="C242" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D242" s="11" t="n">
+      <c r="D242" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E242" s="11" t="n">
+      <c r="E242" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F242" s="11" t="inlineStr">
+      <c r="F242" s="13" t="inlineStr">
         <is>
           <t>clear b</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="F243" s="11" t="inlineStr">
+      <c r="F243" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="F244" s="11" t="inlineStr">
+      <c r="F244" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="F245" s="11" t="inlineStr">
+      <c r="F245" s="13" t="inlineStr">
         <is>
           <t>on e d</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="F246" s="11" t="inlineStr">
+      <c r="F246" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="11" t="inlineStr">
+      <c r="A247" s="13" t="inlineStr">
         <is>
           <t>T14</t>
         </is>
       </c>
-      <c r="B247" s="11" t="inlineStr">
+      <c r="B247" s="13" t="inlineStr">
         <is>
           <t>pick_up c</t>
         </is>
       </c>
-      <c r="C247" s="11" t="n">
+      <c r="C247" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D247" s="11" t="n">
+      <c r="D247" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E247" s="11" t="n">
+      <c r="E247" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F247" s="11" t="inlineStr">
+      <c r="F247" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="F248" s="11" t="inlineStr">
+      <c r="F248" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="F249" s="11" t="inlineStr">
+      <c r="F249" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="F250" s="11" t="inlineStr">
+      <c r="F250" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="F251" s="11" t="inlineStr">
+      <c r="F251" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="F252" s="11" t="inlineStr">
+      <c r="F252" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="inlineStr">
+      <c r="A253" s="13" t="inlineStr">
         <is>
           <t>T15</t>
         </is>
       </c>
-      <c r="B253" s="11" t="inlineStr">
+      <c r="B253" s="13" t="inlineStr">
         <is>
           <t>stack c b</t>
         </is>
       </c>
-      <c r="C253" s="11" t="n">
+      <c r="C253" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D253" s="11" t="n">
+      <c r="D253" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E253" s="11" t="n">
+      <c r="E253" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F253" s="11" t="inlineStr">
+      <c r="F253" s="13" t="inlineStr">
         <is>
           <t>on a b</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="F254" s="11" t="inlineStr">
+      <c r="F254" s="13" t="inlineStr">
         <is>
           <t>on b a</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="F255" s="11" t="inlineStr">
+      <c r="F255" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="F256" s="11" t="inlineStr">
+      <c r="F256" s="13" t="inlineStr">
         <is>
           <t>on e d</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="F257" s="11" t="inlineStr">
+      <c r="F257" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="F258" s="11" t="inlineStr">
+      <c r="F258" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="13" t="inlineStr">
+      <c r="A261" s="15" t="inlineStr">
         <is>
           <t>PROBLEM9 — 19 transitions, 188 predicates, 69 FA violations</t>
         </is>
@@ -7935,426 +8029,426 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="11" t="inlineStr">
+      <c r="A264" s="13" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B264" s="11" t="inlineStr">
+      <c r="B264" s="13" t="inlineStr">
         <is>
           <t>unstack b c</t>
         </is>
       </c>
-      <c r="C264" s="11" t="n">
+      <c r="C264" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D264" s="11" t="n">
+      <c r="D264" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E264" s="11" t="n">
+      <c r="E264" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F264" s="11" t="inlineStr">
+      <c r="F264" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="F265" s="11" t="inlineStr">
+      <c r="F265" s="13" t="inlineStr">
         <is>
           <t>on d f</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="F266" s="11" t="inlineStr">
+      <c r="F266" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="11" t="inlineStr">
+      <c r="A267" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B267" s="11" t="inlineStr">
+      <c r="B267" s="13" t="inlineStr">
         <is>
           <t>put_down b</t>
         </is>
       </c>
-      <c r="C267" s="11" t="n">
+      <c r="C267" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D267" s="11" t="n">
+      <c r="D267" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E267" s="11" t="n">
+      <c r="E267" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="F267" s="11" t="inlineStr">
+      <c r="F267" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="F268" s="11" t="inlineStr">
+      <c r="F268" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="F269" s="11" t="inlineStr">
+      <c r="F269" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="F270" s="11" t="inlineStr">
+      <c r="F270" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="F271" s="11" t="inlineStr">
+      <c r="F271" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="F272" s="11" t="inlineStr">
+      <c r="F272" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="F273" s="11" t="inlineStr">
+      <c r="F273" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="F274" s="11" t="inlineStr">
+      <c r="F274" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="F275" s="11" t="inlineStr">
+      <c r="F275" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="11" t="inlineStr">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B276" s="11" t="inlineStr">
+      <c r="B276" s="13" t="inlineStr">
         <is>
           <t>unstack c d</t>
         </is>
       </c>
-      <c r="C276" s="11" t="n">
+      <c r="C276" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D276" s="11" t="n">
+      <c r="D276" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E276" s="11" t="n">
+      <c r="E276" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F276" s="11" t="inlineStr">
+      <c r="F276" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="F277" s="11" t="inlineStr">
+      <c r="F277" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="F278" s="11" t="inlineStr">
+      <c r="F278" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="F279" s="11" t="inlineStr">
+      <c r="F279" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="F280" s="11" t="inlineStr">
+      <c r="F280" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="11" t="inlineStr">
+      <c r="A281" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B281" s="11" t="inlineStr">
+      <c r="B281" s="13" t="inlineStr">
         <is>
           <t>put_down c</t>
         </is>
       </c>
-      <c r="C281" s="11" t="n">
+      <c r="C281" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D281" s="11" t="n">
+      <c r="D281" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E281" s="11" t="n">
+      <c r="E281" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F281" s="11" t="inlineStr">
+      <c r="F281" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="F282" s="11" t="inlineStr">
+      <c r="F282" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="F283" s="11" t="inlineStr">
+      <c r="F283" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="F284" s="11" t="inlineStr">
+      <c r="F284" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="F285" s="11" t="inlineStr">
+      <c r="F285" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="F286" s="11" t="inlineStr">
+      <c r="F286" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="11" t="inlineStr">
+      <c r="A287" s="13" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B287" s="11" t="inlineStr">
+      <c r="B287" s="13" t="inlineStr">
         <is>
           <t>unstack d e</t>
         </is>
       </c>
-      <c r="C287" s="11" t="n">
+      <c r="C287" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D287" s="11" t="n">
+      <c r="D287" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E287" s="11" t="n">
+      <c r="E287" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F287" s="11" t="inlineStr">
+      <c r="F287" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="F288" s="11" t="inlineStr">
+      <c r="F288" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="11" t="inlineStr">
+      <c r="A289" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B289" s="11" t="inlineStr">
+      <c r="B289" s="13" t="inlineStr">
         <is>
           <t>put_down d</t>
         </is>
       </c>
-      <c r="C289" s="11" t="n">
+      <c r="C289" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D289" s="11" t="n">
+      <c r="D289" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E289" s="11" t="n">
+      <c r="E289" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F289" s="11" t="inlineStr">
+      <c r="F289" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -8485,675 +8579,675 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="11" t="inlineStr">
+      <c r="A294" s="13" t="inlineStr">
         <is>
           <t>T11</t>
         </is>
       </c>
-      <c r="B294" s="11" t="inlineStr">
+      <c r="B294" s="13" t="inlineStr">
         <is>
           <t>pick_up e</t>
         </is>
       </c>
-      <c r="C294" s="11" t="n">
+      <c r="C294" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D294" s="11" t="n">
+      <c r="D294" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E294" s="11" t="n">
+      <c r="E294" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F294" s="11" t="inlineStr">
+      <c r="F294" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="F295" s="11" t="inlineStr">
+      <c r="F295" s="13" t="inlineStr">
         <is>
           <t>on a f</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="F296" s="11" t="inlineStr">
+      <c r="F296" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="F297" s="11" t="inlineStr">
+      <c r="F297" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="11" t="inlineStr">
+      <c r="A298" s="13" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="B298" s="11" t="inlineStr">
+      <c r="B298" s="13" t="inlineStr">
         <is>
           <t>stack e f</t>
         </is>
       </c>
-      <c r="C298" s="11" t="n">
+      <c r="C298" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D298" s="11" t="n">
+      <c r="D298" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E298" s="11" t="n">
+      <c r="E298" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F298" s="11" t="inlineStr">
+      <c r="F298" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="11" t="inlineStr">
+      <c r="A299" s="13" t="inlineStr">
         <is>
           <t>T13</t>
         </is>
       </c>
-      <c r="B299" s="11" t="inlineStr">
+      <c r="B299" s="13" t="inlineStr">
         <is>
           <t>pick_up d</t>
         </is>
       </c>
-      <c r="C299" s="11" t="n">
+      <c r="C299" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D299" s="11" t="n">
+      <c r="D299" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E299" s="11" t="n">
+      <c r="E299" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F299" s="11" t="inlineStr">
+      <c r="F299" s="13" t="inlineStr">
         <is>
           <t>clear e</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="F300" s="11" t="inlineStr">
+      <c r="F300" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="F301" s="11" t="inlineStr">
+      <c r="F301" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="F302" s="11" t="inlineStr">
+      <c r="F302" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="11" t="inlineStr">
+      <c r="A303" s="13" t="inlineStr">
         <is>
           <t>T14</t>
         </is>
       </c>
-      <c r="B303" s="11" t="inlineStr">
+      <c r="B303" s="13" t="inlineStr">
         <is>
           <t>stack d e</t>
         </is>
       </c>
-      <c r="C303" s="11" t="n">
+      <c r="C303" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D303" s="11" t="n">
+      <c r="D303" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E303" s="11" t="n">
+      <c r="E303" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F303" s="11" t="inlineStr">
+      <c r="F303" s="13" t="inlineStr">
         <is>
           <t>on d a</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="F304" s="11" t="inlineStr">
+      <c r="F304" s="13" t="inlineStr">
         <is>
           <t>on e a</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="F305" s="11" t="inlineStr">
+      <c r="F305" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="F306" s="11" t="inlineStr">
+      <c r="F306" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="11" t="inlineStr">
+      <c r="A307" s="13" t="inlineStr">
         <is>
           <t>T15</t>
         </is>
       </c>
-      <c r="B307" s="11" t="inlineStr">
+      <c r="B307" s="13" t="inlineStr">
         <is>
           <t>pick_up c</t>
         </is>
       </c>
-      <c r="C307" s="11" t="n">
+      <c r="C307" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D307" s="11" t="n">
+      <c r="D307" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E307" s="11" t="n">
+      <c r="E307" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F307" s="11" t="inlineStr">
+      <c r="F307" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="F308" s="11" t="inlineStr">
+      <c r="F308" s="13" t="inlineStr">
         <is>
           <t>on d f</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="F309" s="11" t="inlineStr">
+      <c r="F309" s="13" t="inlineStr">
         <is>
           <t>on e a</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="F310" s="11" t="inlineStr">
+      <c r="F310" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="F311" s="11" t="inlineStr">
+      <c r="F311" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="F312" s="11" t="inlineStr">
+      <c r="F312" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="11" t="inlineStr">
+      <c r="A313" s="13" t="inlineStr">
         <is>
           <t>T16</t>
         </is>
       </c>
-      <c r="B313" s="11" t="inlineStr">
+      <c r="B313" s="13" t="inlineStr">
         <is>
           <t>stack c d</t>
         </is>
       </c>
-      <c r="C313" s="11" t="n">
+      <c r="C313" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D313" s="11" t="n">
+      <c r="D313" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E313" s="11" t="n">
+      <c r="E313" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F313" s="11" t="inlineStr">
+      <c r="F313" s="13" t="inlineStr">
         <is>
           <t>on a f</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="F314" s="11" t="inlineStr">
+      <c r="F314" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="F315" s="11" t="inlineStr">
+      <c r="F315" s="13" t="inlineStr">
         <is>
           <t>on e d</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="F316" s="11" t="inlineStr">
+      <c r="F316" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="F317" s="11" t="inlineStr">
+      <c r="F317" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="F318" s="11" t="inlineStr">
+      <c r="F318" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="F319" s="11" t="inlineStr">
+      <c r="F319" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="F320" s="11" t="inlineStr">
+      <c r="F320" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="11" t="inlineStr">
+      <c r="A321" s="13" t="inlineStr">
         <is>
           <t>T17</t>
         </is>
       </c>
-      <c r="B321" s="11" t="inlineStr">
+      <c r="B321" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C321" s="11" t="n">
+      <c r="C321" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D321" s="11" t="n">
+      <c r="D321" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E321" s="11" t="n">
+      <c r="E321" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F321" s="11" t="inlineStr">
+      <c r="F321" s="13" t="inlineStr">
         <is>
           <t>clear c</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="F322" s="11" t="inlineStr">
+      <c r="F322" s="13" t="inlineStr">
         <is>
           <t>clear d</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="F323" s="11" t="inlineStr">
+      <c r="F323" s="13" t="inlineStr">
         <is>
           <t>on a c</t>
         </is>
       </c>
-      <c r="G323" s="11" t="inlineStr">
+      <c r="G323" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="F324" s="11" t="inlineStr">
+      <c r="F324" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G324" s="11" t="inlineStr">
+      <c r="G324" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="F325" s="11" t="inlineStr">
+      <c r="F325" s="13" t="inlineStr">
         <is>
           <t>ontable a</t>
         </is>
       </c>
-      <c r="G325" s="11" t="inlineStr">
+      <c r="G325" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="F326" s="11" t="inlineStr">
+      <c r="F326" s="13" t="inlineStr">
         <is>
           <t>ontable c</t>
         </is>
       </c>
-      <c r="G326" s="11" t="inlineStr">
+      <c r="G326" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="11" t="inlineStr">
+      <c r="A327" s="13" t="inlineStr">
         <is>
           <t>T18</t>
         </is>
       </c>
-      <c r="B327" s="11" t="inlineStr">
+      <c r="B327" s="13" t="inlineStr">
         <is>
           <t>stack b c</t>
         </is>
       </c>
-      <c r="C327" s="11" t="n">
+      <c r="C327" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D327" s="11" t="n">
+      <c r="D327" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="E327" s="11" t="n">
+      <c r="E327" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="F327" s="11" t="inlineStr">
+      <c r="F327" s="13" t="inlineStr">
         <is>
           <t>clear a</t>
         </is>
       </c>
-      <c r="G327" s="11" t="inlineStr">
+      <c r="G327" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="F328" s="11" t="inlineStr">
+      <c r="F328" s="13" t="inlineStr">
         <is>
           <t>on a f</t>
         </is>
       </c>
-      <c r="G328" s="11" t="inlineStr">
+      <c r="G328" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="F329" s="11" t="inlineStr">
+      <c r="F329" s="13" t="inlineStr">
         <is>
           <t>on c d</t>
         </is>
       </c>
-      <c r="G329" s="11" t="inlineStr">
+      <c r="G329" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="F330" s="11" t="inlineStr">
+      <c r="F330" s="13" t="inlineStr">
         <is>
           <t>on d c</t>
         </is>
       </c>
-      <c r="G330" s="11" t="inlineStr">
+      <c r="G330" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="F331" s="11" t="inlineStr">
+      <c r="F331" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G331" s="11" t="inlineStr">
+      <c r="G331" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="F332" s="11" t="inlineStr">
+      <c r="F332" s="13" t="inlineStr">
         <is>
           <t>on e d</t>
         </is>
       </c>
-      <c r="G332" s="11" t="inlineStr">
+      <c r="G332" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="F333" s="11" t="inlineStr">
+      <c r="F333" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G333" s="11" t="inlineStr">
+      <c r="G333" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="F334" s="11" t="inlineStr">
+      <c r="F334" s="13" t="inlineStr">
         <is>
           <t>on f a</t>
         </is>
       </c>
-      <c r="G334" s="11" t="inlineStr">
+      <c r="G334" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="F335" s="11" t="inlineStr">
+      <c r="F335" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G335" s="11" t="inlineStr">
+      <c r="G335" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="F336" s="11" t="inlineStr">
+      <c r="F336" s="13" t="inlineStr">
         <is>
           <t>ontable a</t>
         </is>
       </c>
-      <c r="G336" s="11" t="inlineStr">
+      <c r="G336" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="13" t="inlineStr">
+      <c r="A339" s="15" t="inlineStr">
         <is>
           <t>PROBLEM10 — 8 transitions, 80 predicates, 12 FA violations</t>
         </is>
@@ -9262,239 +9356,239 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="11" t="inlineStr">
+      <c r="A343" s="13" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B343" s="11" t="inlineStr">
+      <c r="B343" s="13" t="inlineStr">
         <is>
           <t>pick_up d</t>
         </is>
       </c>
-      <c r="C343" s="11" t="n">
+      <c r="C343" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D343" s="11" t="n">
+      <c r="D343" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E343" s="11" t="n">
+      <c r="E343" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F343" s="11" t="inlineStr">
+      <c r="F343" s="13" t="inlineStr">
         <is>
           <t>on e f</t>
         </is>
       </c>
-      <c r="G343" s="11" t="inlineStr">
+      <c r="G343" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="F344" s="11" t="inlineStr">
+      <c r="F344" s="13" t="inlineStr">
         <is>
           <t>on f e</t>
         </is>
       </c>
-      <c r="G344" s="11" t="inlineStr">
+      <c r="G344" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="F345" s="11" t="inlineStr">
+      <c r="F345" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G345" s="11" t="inlineStr">
+      <c r="G345" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="11" t="inlineStr">
+      <c r="A346" s="13" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B346" s="11" t="inlineStr">
+      <c r="B346" s="13" t="inlineStr">
         <is>
           <t>stack d e</t>
         </is>
       </c>
-      <c r="C346" s="11" t="n">
+      <c r="C346" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D346" s="11" t="n">
+      <c r="D346" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E346" s="11" t="n">
+      <c r="E346" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F346" s="11" t="inlineStr">
+      <c r="F346" s="13" t="inlineStr">
         <is>
           <t>clear f</t>
         </is>
       </c>
-      <c r="G346" s="11" t="inlineStr">
+      <c r="G346" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="F347" s="11" t="inlineStr">
+      <c r="F347" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G347" s="11" t="inlineStr">
+      <c r="G347" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="11" t="inlineStr">
+      <c r="A348" s="13" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B348" s="11" t="inlineStr">
+      <c r="B348" s="13" t="inlineStr">
         <is>
           <t>pick_up b</t>
         </is>
       </c>
-      <c r="C348" s="11" t="n">
+      <c r="C348" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D348" s="11" t="n">
+      <c r="D348" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E348" s="11" t="n">
+      <c r="E348" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F348" s="11" t="inlineStr">
+      <c r="F348" s="13" t="inlineStr">
         <is>
           <t>on d e</t>
         </is>
       </c>
-      <c r="G348" s="11" t="inlineStr">
+      <c r="G348" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="F349" s="11" t="inlineStr">
+      <c r="F349" s="13" t="inlineStr">
         <is>
           <t>on d f</t>
         </is>
       </c>
-      <c r="G349" s="11" t="inlineStr">
+      <c r="G349" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="11" t="inlineStr">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B350" s="11" t="inlineStr">
+      <c r="B350" s="13" t="inlineStr">
         <is>
           <t>stack b c</t>
         </is>
       </c>
-      <c r="C350" s="11" t="n">
+      <c r="C350" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D350" s="11" t="n">
+      <c r="D350" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E350" s="11" t="n">
+      <c r="E350" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F350" s="11" t="inlineStr">
+      <c r="F350" s="13" t="inlineStr">
         <is>
           <t>ontable f</t>
         </is>
       </c>
-      <c r="G350" s="11" t="inlineStr">
+      <c r="G350" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="11" t="inlineStr">
+      <c r="A351" s="13" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B351" s="11" t="inlineStr">
+      <c r="B351" s="13" t="inlineStr">
         <is>
           <t>pick_up a</t>
         </is>
       </c>
-      <c r="C351" s="11" t="n">
+      <c r="C351" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D351" s="11" t="n">
+      <c r="D351" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E351" s="11" t="n">
+      <c r="E351" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F351" s="11" t="inlineStr">
+      <c r="F351" s="13" t="inlineStr">
         <is>
           <t>clear b</t>
         </is>
       </c>
-      <c r="G351" s="11" t="inlineStr">
+      <c r="G351" s="13" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="F352" s="11" t="inlineStr">
+      <c r="F352" s="13" t="inlineStr">
         <is>
           <t>ontable b</t>
         </is>
       </c>
-      <c r="G352" s="11" t="inlineStr">
+      <c r="G352" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="F353" s="11" t="inlineStr">
+      <c r="F353" s="13" t="inlineStr">
         <is>
           <t>ontable d</t>
         </is>
       </c>
-      <c r="G353" s="11" t="inlineStr">
+      <c r="G353" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="F354" s="11" t="inlineStr">
+      <c r="F354" s="13" t="inlineStr">
         <is>
           <t>ontable e</t>
         </is>
       </c>
-      <c r="G354" s="11" t="inlineStr">
+      <c r="G354" s="13" t="inlineStr">
         <is>
           <t>FP</t>
         </is>

--- a/blocks_trajectory_gt_confusion.xlsx
+++ b/blocks_trajectory_gt_confusion.xlsx
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
         </is>
       </c>
     </row>
@@ -944,62 +944,62 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -1016,62 +1016,62 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -1088,62 +1088,62 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -1419,10 +1419,10 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1590,7 +1590,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
         </is>
       </c>
     </row>
@@ -1612,14 +1612,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1629,32 +1629,32 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -1988,24 +1988,24 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>TP=3 FP=0
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>TP=3 FP=0
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
           <t>TP=4 FP=0
@@ -2018,10 +2018,10 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=0 TN=0</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
         </is>
       </c>
     </row>
@@ -2217,62 +2217,62 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -2289,62 +2289,62 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=2
-FN=0 TN=3</t>
+          <t>TP=2 FP=0
+FN=3 TN=0</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=3 TN=0</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=3</t>
+          <t>TP=2 FP=0
+FN=2 TN=0</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -2848,90 +2848,90 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>TP=3 FP=0
+          <t>TP=1 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
 FN=2 TN=0</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>clear(x)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>TP=3 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>clear(x)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=3 TN=0</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -2958,14 +2958,14 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -2975,32 +2975,32 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
+          <t>TP=2 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
+          <t>TP=4 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -3027,15 +3027,15 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
+          <t>TP=2 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
+          <t>TP=1 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
@@ -3046,36 +3046,36 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=4
+          <t>TP=4 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
+          <t>TP=2 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
+          <t>TP=2 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=1 TN=0
 SW=0</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=2 TN=0
 SW=0</t>
         </is>
       </c>
